--- a/sitepreview/trust/CodeSystem-Domains.xlsx
+++ b/sitepreview/trust/CodeSystem-Domains.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-05-19T11:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
